--- a/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.10_b0.10_x0.10_Q100_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.10_b0.10_x0.10_Q100_LO.xlsx
@@ -455,13 +455,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.009510738477897173</v>
+        <v>0.008416885587149307</v>
       </c>
       <c r="C2" t="n">
-        <v>0.009510738477897173</v>
+        <v>0.008416885587149307</v>
       </c>
       <c r="D2" t="n">
-        <v>0.002639915568735353</v>
+        <v>0.002531856287778189</v>
       </c>
     </row>
     <row r="3">
@@ -469,13 +469,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.02550142806624176</v>
+        <v>0.02320021990840206</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02550142806624176</v>
+        <v>0.02320021990840206</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006253068781662244</v>
+        <v>0.005964907774998781</v>
       </c>
     </row>
     <row r="4">
@@ -483,13 +483,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.05303393179771231</v>
+        <v>0.0479767361450674</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05303393179771231</v>
+        <v>0.0479767361450674</v>
       </c>
       <c r="D4" t="n">
-        <v>0.005290131858263008</v>
+        <v>0.005083442009435238</v>
       </c>
     </row>
     <row r="5">
@@ -497,13 +497,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.07209979049817691</v>
+        <v>0.0653281629159037</v>
       </c>
       <c r="C5" t="n">
-        <v>0.07209979049817691</v>
+        <v>0.0653281629159037</v>
       </c>
       <c r="D5" t="n">
-        <v>0.008435143867387078</v>
+        <v>0.007486235323711289</v>
       </c>
     </row>
     <row r="6">
@@ -511,13 +511,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.06993241259842045</v>
+        <v>0.06324359777142967</v>
       </c>
       <c r="C6" t="n">
-        <v>0.06993241259842045</v>
+        <v>0.06324359777142967</v>
       </c>
       <c r="D6" t="n">
-        <v>0.008922865651281725</v>
+        <v>0.007244800219595525</v>
       </c>
     </row>
     <row r="7">
@@ -525,13 +525,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0630015605306324</v>
+        <v>0.05704540209869485</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0630015605306324</v>
+        <v>0.05704540209869485</v>
       </c>
       <c r="D7" t="n">
-        <v>0.008434648012504924</v>
+        <v>0.006876650640743602</v>
       </c>
     </row>
     <row r="8">
@@ -539,13 +539,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.05689701993995847</v>
+        <v>0.05159182238716223</v>
       </c>
       <c r="C8" t="n">
-        <v>0.05689701993995847</v>
+        <v>0.05159182238716223</v>
       </c>
       <c r="D8" t="n">
-        <v>0.008387337558150708</v>
+        <v>0.006815746739486109</v>
       </c>
     </row>
     <row r="9">
@@ -553,13 +553,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.05310230785117069</v>
+        <v>0.04819652470356873</v>
       </c>
       <c r="C9" t="n">
-        <v>0.05310230785117069</v>
+        <v>0.04819652470356873</v>
       </c>
       <c r="D9" t="n">
-        <v>0.008718021219346008</v>
+        <v>0.007275295078781505</v>
       </c>
     </row>
   </sheetData>
